--- a/ThinkITAM/Resources/Template/AssetTemplate.xlsx
+++ b/ThinkITAM/Resources/Template/AssetTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yaobu\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YAOBUS\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3827FDF5-55F1-4228-8775-65748E93D854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8C4F871-AF1B-45F6-9957-FB70BC7639F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Asset" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,8 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>购置日期</t>
+          <t>购置日期
+格式：2024/6/6</t>
         </r>
       </text>
     </comment>
@@ -232,6 +233,21 @@
             <charset val="134"/>
           </rPr>
           <t>自定义标签F</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{2B479803-5672-449E-A94C-5F628B9663D2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>请勿修改表头，否则无法导入数据，甚至导致程序出现不可预知的错误</t>
         </r>
       </text>
     </comment>
@@ -289,7 +305,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -309,6 +325,12 @@
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -334,9 +356,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="31" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -671,13 +695,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
     <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" bestFit="1" customWidth="1"/>
@@ -686,9 +710,10 @@
     <col min="10" max="11" width="5.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
@@ -731,10 +756,56 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>